--- a/data/daily/2026-09/2026-09-27.xlsx
+++ b/data/daily/2026-09/2026-09-27.xlsx
@@ -1245,14 +1245,39 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1292,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1317,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1342,17 +1367,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1367,35 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="323850" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1500,27 +1500,52 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1528,74 +1553,74 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1603,54 +1628,29 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="866775" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1905,7 +1905,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="457200" cy="457200"/>
+    <ext cx="457200" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2160,7 +2160,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="1238250"/>
+    <ext cx="1238250" cy="1190625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2596,21 +2596,21 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16139</v>
+        <v>16141</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>뛰어난 피로 회복 효과 — 체력이 필요하거나 피로를 해소하는 데 빠른 도움을 줌</t>
+          <t>피로 회복 및 체력 증진 — 피로 회복에 도움을 주며 체력이 필요한 날 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>선물용으로높은 만족도 — 받는 사람이 기분 좋아하며 지인 생일 선물용으로 적합함</t>
+          <t>선물용으로 높은 만족도 — 받는 사람의 만족도가 높아 생일이나 명절 선물로 적합함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>신속한 배송 서비스 — 주문 후 배송 처리가 빠르게 진행되어 만족스러움</t>
+          <t>빠른 배송 및 공유 편의성 — 배송이 빠르며 수량이 여러 개라 주변 사람들과 나눠 먹기 용이함</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -2655,21 +2655,21 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15465</v>
+        <v>15468</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>편안하고 쉬운 섭취 — 액상이 연하고 주스 같아 목넘김이 편하며 알약 크기가 작음</t>
+          <t>고급스러운 포장과 수량 — 포장이 고급스럽고 추가 수량이 제공되어 선물 구성 만족도가 높음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>피로 해소 및 컨디션 관리 — 피곤하거나 컨디션이 저하되었을 때 기력 보충에 효과적임</t>
+          <t>피로 개선 및 간편한 복용 — 컨디션 저하 시 피로감을 줄여주며 하루 한 포씩 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>선물용 우수한 만족도 — 부모님이나 지인 건강 선물용으로 주고받기에 좋음</t>
+          <t>부담 없는 맛과 목넘김 — 액상이 연해 속이 쓰리지 않고 정제 크기가 작아 목넘김이 편함</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2714,22 +2714,22 @@
         <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3368</v>
+        <v>3369</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>활력 증진 및 피로 개선 — 마신 후 피로감이 줄고 일할 때 생기와 활력이 생김</t>
+          <t>피로 감소 및 활력 증진 — 섭취 후 피곤함이 줄어들고 일할 때 활력과 생기를 더해줌</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>부담 없는 명절 선물 — 가격 할인 쿠폰 적용이 가능하며 명절 선물용으로 적합함</t>
+          <t>빠른 배송과 선물 적합성 — 배송이 빠르며 명절이나 가족 선물용으로 부담 없이 주고받기 좋음</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>쇼핑백 포장 상태 불량 — 동봉되어 온 쇼핑백이 구겨지거나 훼손되어 도착함</t>
+          <t>쇼핑백 상태 불량 — 동봉된 쇼핑백 상태가 불량하여 직접 들고 선물하기에 어려움이 있음</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2777,22 +2777,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>피로 해소 및 활력 증진 — 체력 소모가 많은 날 복용 시 에너지를 보충해 줌</t>
+          <t>체력 충전 및 피로 회복 — 피로를 완화하고 활력이 필요할 때 체력을 챙기기 유용함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>개별 포장의 높은 휴대성 — 한 포씩 개별 포장되어 가방이나 책상에 두고 챙기기 편함</t>
+          <t>개별 포장의 휴대 편의성 — 한 포씩 개별 포장되어 가방이나 책상에 두고 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>빠른 배송과 알찬 구성 — 배송이 빠르고 합리적인 가격대에 구매가 가능함</t>
+          <t>빠른 배송과 정성스러운 포장 — 배송이 빠르고 포장 상태가 잘되어 있어 선물용으로 우수함</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>배송 요청사항 미반영 — 사전 요청한 부재 중 위탁 장소 대신 문 앞에 두고 감</t>
+          <t>배송 요청사항 미반영 — 사전 요청한 배송 장소 대신 문 앞에 두고 가 아쉬움이 남음</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -2836,21 +2836,21 @@
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>1680</v>
+        <v>1683</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 효과 — 맛있게 먹을 수 있으며 피로가 빠르게 풀리고 에너지가 생김</t>
+          <t>높은 신뢰도와 고급 포장 — 정관장 브랜드 신뢰도가 높고 포장이 고급스러워 선물하기 좋음</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>예쁜 포장과 선물 적합성 — 패키지가 예쁘고 개별 포장되어 지인 선물용으로 아주 좋음</t>
+          <t>빠른 피로 회복과 좋은 맛 — 맛이 우수하며 섭취 시 피로가 빠르게 풀리는 느낌을 줌</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>높은 브랜드 신뢰도 — 정관장 브랜드 제품이라 안심하고 신뢰하여 복용함</t>
+          <t>빠른 배송과 개별 포장 — 배송이 매우 빠르며 개별 포장되어 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -2899,21 +2899,29 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>피로 감소 및 편한 섭취 — 꾸준히 복용 시 피로가 덜하며 사무실 등에서 간편하게 먹기 좋음</t>
+          <t>피로 완화 및 선물 만족도 — 피로감을 줄여주며 옵션 선택이 가능해 생일이나 명절 선물로 적합함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>정성스러운 선물 패키징 — 선물용 포장과 패키지 구성이 세심하고 고급스러움</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>정성스러운 패키지 및 배송 — 선물 패키징이 정성스럽고 배송 속도가 빠름</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>간편한 올인원 복용 방식 — 캡슐과 액상이 같이 구성되어 매일 하나씩 간편하게 챙겨 먹기 편함</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>제품 오염 및 스티커 훼손 — 상자와 쇼핑백에 먼지가 가득하거나 밀봉 스티커가 떼어진 채 도착함</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
+          <t>스티커 밀봉 상태 불량 — 밀봉 스티커가 반쯤 떼어져 있거나 표면에 손자국 및 이물질이 남아 있음</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>제품 외관 청결 미흡 — 배송된 상자와 쇼핑백에 먼지가 가득 묻어 있어 검수가 아쉬움</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
@@ -2958,17 +2966,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>알차고 넉넉한 제품 구성 — 한 달 치 넉넉한 수량과 알찬 구성으로 든든함</t>
+          <t>알찬 구성과 넉넉한 용량 — 한 달 치 넉넉한 양과 알찬 구성으로 든든하게 섭취할 수 있음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>빠른 배송 및 쇼핑백 증정 — 연휴에도 배송이 빠르며 선물용 쇼핑백을 함께 제공함</t>
+          <t>빠른 배송과 쇼핑백 증정 — 명절 연휴에도 배송이 빠르고 쇼핑백이 포함되어 선물하기 좋음</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>선물용으로 높은 감동 — 건강을 챙겨주는 마음이 전달되어 선물 만족도가 높음</t>
+          <t>뛰어난 피로 개선 효과 — 섭취 후 피로가 줄고 활력이 생겨 제품 만족도가 높음</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -3013,21 +3021,21 @@
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>8727</v>
+        <v>8728</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>물 없는 듀얼 제형 섭취 — 액상과 정제가 같이 있어 물 없이도 언제 어디서나 간편히 섭취함</t>
+          <t>물 없이 먹는 듀얼 제형 — 액상과 정제가 함께 있어 물 없이도 언제 어디서나 간편하게 섭취함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>상큼한 맛과 활력 증진 — 오렌지 맛으로 맛있게 마실 수 있으며 활력 충전에 도움이 됨</t>
+          <t>활력 증진 및 상큼한 맛 — 피로 회복에 도움을 주고 상큼한 오렌지 맛으로 맛있게 먹을 수 있음</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>예쁘고 꼼꼼한 포장 — 패키지 디자인이 예쁘고 배송 포장이 꼼꼼하게 도착함</t>
+          <t>예쁜 패키지와 높은 휴대성 — 포장 케이스가 예쁘고 개별 포장되어 들고 다니며 선물하거나 먹기 좋음</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -3076,22 +3084,22 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>깔끔한 선물용 패키징 — 선물 받는 느낌을 주는 정성스럽고 깔끔한 포장 상태임</t>
+          <t>성별 맞춤 영양 구성 — 성별에 맞춘 옵션 선택이 가능하며 다양한 영양 성분을 함유함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>성별 맞춤 영양 설계 — 남성용과 여성용 제품 선택이 가능하여 영양을 세심하게 챙김</t>
+          <t>정성스럽고 깔끔한 포장 — 포장이 깔끔하고 고급스러워 선물용으로 높은 만족감을 줌</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>지속적인 피로 개선 — 꾸준히 먹으면 피로감이 줄어들고 컨디션 유지에 도움 됨</t>
+          <t>피로 완화 및 간편한 복용 — 지속적으로 섭취 시 덜 피로하며 복용 방식이 간편함</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>다소 큰 알약 크기 — 기존 제품에 비해 정제 크기가 커서 삼키기 다소 불편함</t>
+          <t>큰 알약 크기의 목넘김 부담 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 힘듦</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -3139,17 +3147,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>맛있고 편리한 구미 제형 — 맛있는 젤리 형태라 물 없이도 간편하게 섭취 가능함</t>
+          <t>맛있는 구미 제형의 편리함 — 젤리 제형으로 물 없이도 맛있고 간단하게 섭취할 수 있음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>귀여운 증정품과 포장 — 귀여운 키캡 증정과 아기자기한 포장으로 가볍게 선물하기 좋음</t>
+          <t>귀엽고 깔끔한 선물 패키지 — 포장이 귀엽고 깔끔하여 가볍게 선물하기 적합함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>용이한 지속 복용성 — 거부감이 없는 맛과 형태 덕분에 매일 꾸준히 챙겨 먹기 수월함</t>
+          <t>꾸준한 섭취 편의성 — 거부감 없는 맛 덕분에 매일 잊지 않고 잘 챙겨 먹게 됨</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -3198,18 +3206,22 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>고급스러운 포장 디자인 — 보자기, 틴케이스, 쇼핑백 등 선물 포장이 매우 예쁘고 정성스러움</t>
+          <t>고급스러운 선물 포장 — 틴케이스와 보자기, 쇼핑백 등 정성스럽고 예쁜 포장을 제공함</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>비리지 않은 상큼한 맛 — 콜라겐 특유의 비린 맛이 없고 맛있게 앰플 형태로 섭취함</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>비리지 않고 맛있는 앰플 — 콜라겐 특유의 비린 맛이 없고 맛있게 섭취할 수 있음</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>휴대와 복용이 간편함 — 앰플 낱개 개별 포장 형태로 섭취 및 휴대가 용이함</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>높고 상승하는 가격대 — 가격대가 다소 높은 편이며 지속적으로 가격이 올라 부담스러움</t>
+          <t>높은 가격대에 대한 부담 — 제품 품질은 우수하나 가격대가 다소 높게 느껴짐</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -3257,17 +3269,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>편안한 소화 촉진 효과 — 식후 복용 시 더부룩함이 사라지고 속이 편안해짐</t>
+          <t>속이 편안한 소화 개선 — 식후 복용 시 소화를 돕고 속을 편안하게 해주며 배변 활동에 이로움</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>구수하고 맛있는 풍미 — 고구마 맛 등으로 거부감 없이 맛있게 먹기 좋음</t>
+          <t>고소하고 부담 없는 맛 — 고구마 맛이 나며 자극적이지 않아 거부감 없이 먹기 좋음</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>풍부한 혜택과 빠른 배송 — 사은품 증정 구성이 풍성하고 배송 처리가 신속함</t>
+          <t>빠른 배송과 풍부한 혜택 — 배송이 빠르고 증정품이 많으며 구매 가격 혜택이 훌륭함</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -3277,7 +3289,7 @@
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3285,53 +3297,53 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>64,200원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/14208051</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260908134122_cb4724fa4d2d4e45b370faede2a463a5.jpg</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>맛있는 소스와 부드러운 식감 — 뻑뻑하지 않고 부드러우며 소스가 맛있어 질리지 않고 다이어트 가능함</t>
+          <t>포토카드 및 풍성한 사은품 — 아티스트 포토카드와 단백질바 등 알찬 구성품을 제공함</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>다양하고 알찬 제품 구성 — 스테이크, 주먹밥 등 여러 종류를 골고루 맛볼 수 있음</t>
+          <t>더부룩함 완화 및 속 편함 — 식후 섭취 시 더부룩함이 줄어들고 매일 속이 편안해짐</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 저렴한 가격으로 다량의 제품을 구매할 수 있어 만족스러움</t>
+          <t>고소하고 맛있는 말차 맛 — 효소 특유의 역함 없이 고소하고 맛있는 베리말차 맛을 즐길 수 있음</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>배송 중 제품 해동 — 냉동 배송되어야 할 제품이 전부 녹아 도착함</t>
+          <t>다소 아쉬운 배송 속도 — 구성품은 만족스러우나 배송 일정이 약간 늦은 편임</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -3340,7 +3352,7 @@
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3348,49 +3360,53 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>64,200원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14208051</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260908134122_cb4724fa4d2d4e45b370faede2a463a5.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>아이돌 포카 및 풍성한 구성 — 원하는 멤버 포토카드 증정과 단백질바 포함 구성이 알참</t>
+          <t>부드러운 식감과 다양한 맛 — 닭가슴살이 부드럽고 소스 및 종류가 다양하여 질리지 않음</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>맛있고 속 편한 효과 — 꼬소하고 맛이 좋으며 식후 더부룩한 속을 편하게 해줌</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>뛰어난 가성비 및 구성 — 저렴한 가격에 다채로운 구성으로 구매할 수 있어 경제적임</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>꼼꼼한 포장과 빠른 배송 — 제품 포장이 꼼꼼하고 배송이 신속하게 도착함</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>다소 아쉬운 배송 속도 — 주문 후 배송 완료까지 시간이 다소 느린 편임</t>
+          <t>배송 중 제품 해동 발생 — 배송 과정에서 내용물이 다 녹아서 도착하는 문제점이 있음</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -3438,17 +3454,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>비리지 않은 깔끔한 맛 — 단백질 음료 특유의 비린 맛이나 텁텁함 없이 달콤하고 부드러움</t>
+          <t>비리지 않고 달콤한 맛 — 단백질 특유의 텁텁함이나 비린 맛이 없고 음료처럼 부드럽고 달콤함</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>편리한 휴대 및 파우치 — 슬림한 패키지 덕분에 가방에 넣고 다니며 먹기 용이함</t>
+          <t>운동 후 간편한 단백질 보충 — 운동 직후나 간식 대용으로 챙겨 먹기 좋아 포만감과 영양을 챙김</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>운동 후 영양 보충 적합 — 당류 부담이 적고 포만감을 주어 운동 후 허기 채우기에 좋음</t>
+          <t>슬림한 용기와 편리한 휴대 — 가방에 넣기 좋은 슬림한 용기 형태로 언제 어디서나 마시기 편함</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -3497,20 +3513,24 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>화려하고 예쁜 포장 — 패키지와 케이스 포장이 공주풍으로 고급스럽고 예쁨</t>
+          <t>예쁘고 고급스러운 패키지 — 패키지 디자인이 예쁘고 고급스러워 선물 받았을 때 기분이 좋아짐</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>새콤달콤 맛있는 풍미 — 비타민 음료 맛과 유사하여 거부감 없이 맛있게 먹기 좋음</t>
+          <t>새콤하고 맛있는 앰플 타입 — 새콤달콤하고 건강한 맛이라 거부감 없이 맛있게 먹기 좋음</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>간편한 앰플 제형 — 하나씩 따서 간편하게 먹을 수 있는 앰플 형태임</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>간편한 따서 마시는 제형 — 마시는 앰플 형태로 개봉하여 바로 섭취할 수 있어 편리함</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>단기 복용 시 효과 미체감 — 단기간 먹었을 때는 눈에 띄는 효과를 느끼기 어려움</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
@@ -3525,48 +3545,48 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[좋은 아침 선물] 진저샷 미니보틀 8개입 (메시지 참 증정)</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>타이거모닝</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>29,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13586002</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260512190926_6c62df625cf44ea9ad3d7797fa43588b.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>상큼하고 매력적인 맛 — 생강과 과일 원료가 어우러져 부담 없이 상큼하게 즐김</t>
+          <t>휴대하기 편한 개별 스틱 — 작은 스틱 포장으로 물 없이 어디서나 간편하게 먹을 수 있음</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>에너지 충전 및 기분 전환 — 공복이나 피곤할 때 마시면 눈이 뜨이고 활력이 충전됨</t>
+          <t>고급스러운 선물 패키지 — 패키지와 쇼핑백 구성이 고급스러워 모임이나 선물용으로 적합함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>귀여운 용기 패키지 — 미니 보틀 디자인이 귀여워 챙겨 먹는 재미가 있음</t>
+          <t>확실한 숙취 완화 효과 — 음주 전후 복용 시 다음 날 숙취와 몸의 무거움을 덜어줌</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3615,17 +3635,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>뛰어난 활력 증진 효과 — 초고함량 아르기닌 함유로 운동 퍼포먼스 상승 및 피로 개선에 효과적임</t>
+          <t>초고함량 아르기닌의 효과 — 6,200mg 고함량으로 운동 전후 및 피로 해소와 활력 증진에 도움 됨</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>간편한 개별 스틱 포장 — 하루 1포 개별 스틱으로 휴대성이 좋고 복용이 편리함</t>
+          <t>고급스러운 패키지 증정 — 고급스러운 포장 디자인, 쇼핑백, 추가 스틱이 함께 제공됨</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>고급 패키지 및 추가 증정 — 블랙&amp;레드 패키지가 고급스럽고 추가 증정 스틱과 쇼핑백 구성이 알참</t>
+          <t>간편한 1포 섭취와 휴대성 — 하루 한 포씩 개별 포장되어 있어 휴대하며 챙겨 먹기 편리함</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3643,48 +3663,48 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>[좋은 아침 선물] 진저샷 미니보틀 8개입 (메시지 참 증정)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>타이거모닝</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>29,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/13586002</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260512190926_6c62df625cf44ea9ad3d7797fa43588b.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 효과 — 음주 전후 복용 시 다음날 특유의 무겁고 늘어지는 숙취가 완화됨</t>
+          <t>생강과 과일의 상큼한 조화 — 생강 맛을 과일로 아우러 부담 없이 상큼하고 맛있게 마실 수 있음</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>휴대가 용이한 개별 스틱 — 물 없이 먹을 수 있는 컴팩트한 스틱 형태로 술자리 휴대가 편함</t>
+          <t>귀여운 보틀 디자인 — 미니 보틀 디자인이 귀여워 손이 잘 가며 기분 전환에 도움을 줌</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>고급스러운 보라색 패키지 — 포장이 고급스럽고 깔끔하여 지인 선물용으로 적합함</t>
+          <t>아침 활력 충전 및 목 건강 — 환절기 목 잠김을 완화하고 공복에도 부담 없이 아침 에너지를 채워줌</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3694,7 +3714,7 @@
     <row r="21" ht="38" customHeight="1">
       <c r="B21" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3702,12 +3722,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>랩노쉬</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3717,33 +3737,33 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12052312</t>
+          <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260723171929_09161ef5007a47039ea2ea7988556deb.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>15</v>
+        <v>1534</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>다양한 베스트 모음 구성 — 드링크, 쿠키, 쿠키바 등 여러 베스트 제품을 한 번에 체험함</t>
+          <t>아르기닌과 밀크씨슬 조합 — 활력과 간 건강을 동시 케어할 수 있는 2개월분 세트 구성이 우수함</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>디저트 같은 뛰어난 맛 — 프로틴 제품임에도 불구하고 매우 맛있고 달콤함</t>
+          <t>피로 회복 및 운동 컨디션 — 섭취 후 아침 피로가 줄고 운동 집중도와 컨디션 유지에 도움이 됨</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>선물용 우수한 패키징 — 패키지가 고퀄리티이고 큼직해 이벤트 경품이나 선물용으로 제격임</t>
+          <t>쇼핑백 포함과 브랜드 신뢰 — 김종국 추천 제품으로 신뢰가 가며 쇼핑백이 포함되어 선물하기 좋음</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -4068,19 +4088,19 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16139</v>
+        <v>16141</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15465</v>
+        <v>15468</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3368</v>
+        <v>3369</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>796</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1680</v>
+        <v>1683</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>214</v>
@@ -4089,7 +4109,7 @@
         <v>779</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>8727</v>
+        <v>8728</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>772</v>
@@ -4106,74 +4126,75 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 피로 회복 효과 — 체력이 필요하거나 피로를 해소하는 데 빠른 도움을 줌
-선물용으로높은 만족도 — 받는 사람이 기분 좋아하며 지인 생일 선물용으로 적합함
-신속한 배송 서비스 — 주문 후 배송 처리가 빠르게 진행되어 만족스러움</t>
+          <t>피로 회복 및 체력 증진 — 피로 회복에 도움을 주며 체력이 필요한 날 챙겨 먹기 좋음
+선물용으로 높은 만족도 — 받는 사람의 만족도가 높아 생일이나 명절 선물로 적합함
+빠른 배송 및 공유 편의성 — 배송이 빠르며 수량이 여러 개라 주변 사람들과 나눠 먹기 용이함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>편안하고 쉬운 섭취 — 액상이 연하고 주스 같아 목넘김이 편하며 알약 크기가 작음
-피로 해소 및 컨디션 관리 — 피곤하거나 컨디션이 저하되었을 때 기력 보충에 효과적임
-선물용 우수한 만족도 — 부모님이나 지인 건강 선물용으로 주고받기에 좋음</t>
+          <t>고급스러운 포장과 수량 — 포장이 고급스럽고 추가 수량이 제공되어 선물 구성 만족도가 높음
+피로 개선 및 간편한 복용 — 컨디션 저하 시 피로감을 줄여주며 하루 한 포씩 간편하게 섭취 가능함
+부담 없는 맛과 목넘김 — 액상이 연해 속이 쓰리지 않고 정제 크기가 작아 목넘김이 편함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>활력 증진 및 피로 개선 — 마신 후 피로감이 줄고 일할 때 생기와 활력이 생김
-부담 없는 명절 선물 — 가격 할인 쿠폰 적용이 가능하며 명절 선물용으로 적합함</t>
+          <t>피로 감소 및 활력 증진 — 섭취 후 피곤함이 줄어들고 일할 때 활력과 생기를 더해줌
+빠른 배송과 선물 적합성 — 배송이 빠르며 명절이나 가족 선물용으로 부담 없이 주고받기 좋음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>피로 해소 및 활력 증진 — 체력 소모가 많은 날 복용 시 에너지를 보충해 줌
-개별 포장의 높은 휴대성 — 한 포씩 개별 포장되어 가방이나 책상에 두고 챙기기 편함
-빠른 배송과 알찬 구성 — 배송이 빠르고 합리적인 가격대에 구매가 가능함</t>
+          <t>체력 충전 및 피로 회복 — 피로를 완화하고 활력이 필요할 때 체력을 챙기기 유용함
+개별 포장의 휴대 편의성 — 한 포씩 개별 포장되어 가방이나 책상에 두고 챙겨 먹기 편함
+빠른 배송과 정성스러운 포장 — 배송이 빠르고 포장 상태가 잘되어 있어 선물용으로 우수함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 효과 — 맛있게 먹을 수 있으며 피로가 빠르게 풀리고 에너지가 생김
-예쁜 포장과 선물 적합성 — 패키지가 예쁘고 개별 포장되어 지인 선물용으로 아주 좋음
-높은 브랜드 신뢰도 — 정관장 브랜드 제품이라 안심하고 신뢰하여 복용함</t>
+          <t>높은 신뢰도와 고급 포장 — 정관장 브랜드 신뢰도가 높고 포장이 고급스러워 선물하기 좋음
+빠른 피로 회복과 좋은 맛 — 맛이 우수하며 섭취 시 피로가 빠르게 풀리는 느낌을 줌
+빠른 배송과 개별 포장 — 배송이 매우 빠르며 개별 포장되어 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>피로 감소 및 편한 섭취 — 꾸준히 복용 시 피로가 덜하며 사무실 등에서 간편하게 먹기 좋음
-정성스러운 선물 패키징 — 선물용 포장과 패키지 구성이 세심하고 고급스러움</t>
+          <t>피로 완화 및 선물 만족도 — 피로감을 줄여주며 옵션 선택이 가능해 생일이나 명절 선물로 적합함
+정성스러운 패키지 및 배송 — 선물 패키징이 정성스럽고 배송 속도가 빠름
+간편한 올인원 복용 방식 — 캡슐과 액상이 같이 구성되어 매일 하나씩 간편하게 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>알차고 넉넉한 제품 구성 — 한 달 치 넉넉한 수량과 알찬 구성으로 든든함
-빠른 배송 및 쇼핑백 증정 — 연휴에도 배송이 빠르며 선물용 쇼핑백을 함께 제공함
-선물용으로 높은 감동 — 건강을 챙겨주는 마음이 전달되어 선물 만족도가 높음</t>
+          <t>알찬 구성과 넉넉한 용량 — 한 달 치 넉넉한 양과 알찬 구성으로 든든하게 섭취할 수 있음
+빠른 배송과 쇼핑백 증정 — 명절 연휴에도 배송이 빠르고 쇼핑백이 포함되어 선물하기 좋음
+뛰어난 피로 개선 효과 — 섭취 후 피로가 줄고 활력이 생겨 제품 만족도가 높음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>물 없는 듀얼 제형 섭취 — 액상과 정제가 같이 있어 물 없이도 언제 어디서나 간편히 섭취함
-상큼한 맛과 활력 증진 — 오렌지 맛으로 맛있게 마실 수 있으며 활력 충전에 도움이 됨
-예쁘고 꼼꼼한 포장 — 패키지 디자인이 예쁘고 배송 포장이 꼼꼼하게 도착함</t>
+          <t>물 없이 먹는 듀얼 제형 — 액상과 정제가 함께 있어 물 없이도 언제 어디서나 간편하게 섭취함
+활력 증진 및 상큼한 맛 — 피로 회복에 도움을 주고 상큼한 오렌지 맛으로 맛있게 먹을 수 있음
+예쁜 패키지와 높은 휴대성 — 포장 케이스가 예쁘고 개별 포장되어 들고 다니며 선물하거나 먹기 좋음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>깔끔한 선물용 패키징 — 선물 받는 느낌을 주는 정성스럽고 깔끔한 포장 상태임
-성별 맞춤 영양 설계 — 남성용과 여성용 제품 선택이 가능하여 영양을 세심하게 챙김
-지속적인 피로 개선 — 꾸준히 먹으면 피로감이 줄어들고 컨디션 유지에 도움 됨</t>
+          <t>성별 맞춤 영양 구성 — 성별에 맞춘 옵션 선택이 가능하며 다양한 영양 성분을 함유함
+정성스럽고 깔끔한 포장 — 포장이 깔끔하고 고급스러워 선물용으로 높은 만족감을 줌
+피로 완화 및 간편한 복용 — 지속적으로 섭취 시 덜 피로하며 복용 방식이 간편함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>맛있고 편리한 구미 제형 — 맛있는 젤리 형태라 물 없이도 간편하게 섭취 가능함
-귀여운 증정품과 포장 — 귀여운 키캡 증정과 아기자기한 포장으로 가볍게 선물하기 좋음
-용이한 지속 복용성 — 거부감이 없는 맛과 형태 덕분에 매일 꾸준히 챙겨 먹기 수월함</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>맛있는 구미 제형의 편리함 — 젤리 제형으로 물 없이도 맛있고 간단하게 섭취할 수 있음
+귀엽고 깔끔한 선물 패키지 — 포장이 귀엽고 깔끔하여 가볍게 선물하기 적합함
+꾸준한 섭취 편의성 — 거부감 없는 맛 덕분에 매일 잊지 않고 잘 챙겨 먹게 됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4183,25 +4204,26 @@
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>쇼핑백 포장 상태 불량 — 동봉되어 온 쇼핑백이 구겨지거나 훼손되어 도착함</t>
+          <t>쇼핑백 상태 불량 — 동봉된 쇼핑백 상태가 불량하여 직접 들고 선물하기에 어려움이 있음</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>배송 요청사항 미반영 — 사전 요청한 부재 중 위탁 장소 대신 문 앞에 두고 감</t>
+          <t>배송 요청사항 미반영 — 사전 요청한 배송 장소 대신 문 앞에 두고 가 아쉬움이 남음</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>제품 오염 및 스티커 훼손 — 상자와 쇼핑백에 먼지가 가득하거나 밀봉 스티커가 떼어진 채 도착함</t>
+          <t>스티커 밀봉 상태 불량 — 밀봉 스티커가 반쯤 떼어져 있거나 표면에 손자국 및 이물질이 남아 있음
+제품 외관 청결 미흡 — 배송된 상자와 쇼핑백에 먼지가 가득 묻어 있어 검수가 아쉬움</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>다소 큰 알약 크기 — 기존 제품에 비해 정제 크기가 커서 삼키기 다소 불편함</t>
+          <t>큰 알약 크기의 목넘김 부담 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 힘듦</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -4412,42 +4434,42 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -4469,14 +4491,14 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
-        </is>
-      </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
           <t>셀렉스</t>
@@ -4489,22 +4511,22 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
+          <t>알디콤</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
           <t>타이거모닝</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>익스트림</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>알디콤</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>랩노쉬</t>
         </is>
       </c>
     </row>
@@ -4526,14 +4548,14 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
+          <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
           <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
-        </is>
-      </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
           <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
@@ -4546,22 +4568,22 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
           <t>[좋은 아침 선물] 진저샷 미니보틀 8개입 (메시지 참 증정)</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
-        </is>
-      </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
     </row>
@@ -4615,10 +4637,10 @@
         <v>1679</v>
       </c>
       <c r="E19" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>56</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>102</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>215</v>
@@ -4627,16 +4649,16 @@
         <v>759</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>248</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>15</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
@@ -4647,70 +4669,72 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 포장 디자인 — 보자기, 틴케이스, 쇼핑백 등 선물 포장이 매우 예쁘고 정성스러움
-비리지 않은 상큼한 맛 — 콜라겐 특유의 비린 맛이 없고 맛있게 앰플 형태로 섭취함</t>
+          <t>고급스러운 선물 포장 — 틴케이스와 보자기, 쇼핑백 등 정성스럽고 예쁜 포장을 제공함
+비리지 않고 맛있는 앰플 — 콜라겐 특유의 비린 맛이 없고 맛있게 섭취할 수 있음
+휴대와 복용이 간편함 — 앰플 낱개 개별 포장 형태로 섭취 및 휴대가 용이함</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>편안한 소화 촉진 효과 — 식후 복용 시 더부룩함이 사라지고 속이 편안해짐
-구수하고 맛있는 풍미 — 고구마 맛 등으로 거부감 없이 맛있게 먹기 좋음
-풍부한 혜택과 빠른 배송 — 사은품 증정 구성이 풍성하고 배송 처리가 신속함</t>
+          <t>속이 편안한 소화 개선 — 식후 복용 시 소화를 돕고 속을 편안하게 해주며 배변 활동에 이로움
+고소하고 부담 없는 맛 — 고구마 맛이 나며 자극적이지 않아 거부감 없이 먹기 좋음
+빠른 배송과 풍부한 혜택 — 배송이 빠르고 증정품이 많으며 구매 가격 혜택이 훌륭함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>맛있는 소스와 부드러운 식감 — 뻑뻑하지 않고 부드러우며 소스가 맛있어 질리지 않고 다이어트 가능함
-다양하고 알찬 제품 구성 — 스테이크, 주먹밥 등 여러 종류를 골고루 맛볼 수 있음
-뛰어난 가성비 — 저렴한 가격으로 다량의 제품을 구매할 수 있어 만족스러움</t>
+          <t>포토카드 및 풍성한 사은품 — 아티스트 포토카드와 단백질바 등 알찬 구성품을 제공함
+더부룩함 완화 및 속 편함 — 식후 섭취 시 더부룩함이 줄어들고 매일 속이 편안해짐
+고소하고 맛있는 말차 맛 — 효소 특유의 역함 없이 고소하고 맛있는 베리말차 맛을 즐길 수 있음</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>아이돌 포카 및 풍성한 구성 — 원하는 멤버 포토카드 증정과 단백질바 포함 구성이 알참
-맛있고 속 편한 효과 — 꼬소하고 맛이 좋으며 식후 더부룩한 속을 편하게 해줌</t>
+          <t>부드러운 식감과 다양한 맛 — 닭가슴살이 부드럽고 소스 및 종류가 다양하여 질리지 않음
+뛰어난 가성비 및 구성 — 저렴한 가격에 다채로운 구성으로 구매할 수 있어 경제적임
+꼼꼼한 포장과 빠른 배송 — 제품 포장이 꼼꼼하고 배송이 신속하게 도착함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>비리지 않은 깔끔한 맛 — 단백질 음료 특유의 비린 맛이나 텁텁함 없이 달콤하고 부드러움
-편리한 휴대 및 파우치 — 슬림한 패키지 덕분에 가방에 넣고 다니며 먹기 용이함
-운동 후 영양 보충 적합 — 당류 부담이 적고 포만감을 주어 운동 후 허기 채우기에 좋음</t>
+          <t>비리지 않고 달콤한 맛 — 단백질 특유의 텁텁함이나 비린 맛이 없고 음료처럼 부드럽고 달콤함
+운동 후 간편한 단백질 보충 — 운동 직후나 간식 대용으로 챙겨 먹기 좋아 포만감과 영양을 챙김
+슬림한 용기와 편리한 휴대 — 가방에 넣기 좋은 슬림한 용기 형태로 언제 어디서나 마시기 편함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>화려하고 예쁜 포장 — 패키지와 케이스 포장이 공주풍으로 고급스럽고 예쁨
-새콤달콤 맛있는 풍미 — 비타민 음료 맛과 유사하여 거부감 없이 맛있게 먹기 좋음
-간편한 앰플 제형 — 하나씩 따서 간편하게 먹을 수 있는 앰플 형태임</t>
+          <t>예쁘고 고급스러운 패키지 — 패키지 디자인이 예쁘고 고급스러워 선물 받았을 때 기분이 좋아짐
+새콤하고 맛있는 앰플 타입 — 새콤달콤하고 건강한 맛이라 거부감 없이 맛있게 먹기 좋음
+간편한 따서 마시는 제형 — 마시는 앰플 형태로 개봉하여 바로 섭취할 수 있어 편리함</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>상큼하고 매력적인 맛 — 생강과 과일 원료가 어우러져 부담 없이 상큼하게 즐김
-에너지 충전 및 기분 전환 — 공복이나 피곤할 때 마시면 눈이 뜨이고 활력이 충전됨
-귀여운 용기 패키지 — 미니 보틀 디자인이 귀여워 챙겨 먹는 재미가 있음</t>
+          <t>휴대하기 편한 개별 스틱 — 작은 스틱 포장으로 물 없이 어디서나 간편하게 먹을 수 있음
+고급스러운 선물 패키지 — 패키지와 쇼핑백 구성이 고급스러워 모임이나 선물용으로 적합함
+확실한 숙취 완화 효과 — 음주 전후 복용 시 다음 날 숙취와 몸의 무거움을 덜어줌</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 활력 증진 효과 — 초고함량 아르기닌 함유로 운동 퍼포먼스 상승 및 피로 개선에 효과적임
-간편한 개별 스틱 포장 — 하루 1포 개별 스틱으로 휴대성이 좋고 복용이 편리함
-고급 패키지 및 추가 증정 — 블랙&amp;레드 패키지가 고급스럽고 추가 증정 스틱과 쇼핑백 구성이 알참</t>
+          <t>초고함량 아르기닌의 효과 — 6,200mg 고함량으로 운동 전후 및 피로 해소와 활력 증진에 도움 됨
+고급스러운 패키지 증정 — 고급스러운 포장 디자인, 쇼핑백, 추가 스틱이 함께 제공됨
+간편한 1포 섭취와 휴대성 — 하루 한 포씩 개별 포장되어 있어 휴대하며 챙겨 먹기 편리함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 효과 — 음주 전후 복용 시 다음날 특유의 무겁고 늘어지는 숙취가 완화됨
-휴대가 용이한 개별 스틱 — 물 없이 먹을 수 있는 컴팩트한 스틱 형태로 술자리 휴대가 편함
-고급스러운 보라색 패키지 — 포장이 고급스럽고 깔끔하여 지인 선물용으로 적합함</t>
+          <t>생강과 과일의 상큼한 조화 — 생강 맛을 과일로 아우러 부담 없이 상큼하고 맛있게 마실 수 있음
+귀여운 보틀 디자인 — 미니 보틀 디자인이 귀여워 손이 잘 가며 기분 전환에 도움을 줌
+아침 활력 충전 및 목 건강 — 환절기 목 잠김을 완화하고 공복에도 부담 없이 아침 에너지를 채워줌</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>다양한 베스트 모음 구성 — 드링크, 쿠키, 쿠키바 등 여러 베스트 제품을 한 번에 체험함
-디저트 같은 뛰어난 맛 — 프로틴 제품임에도 불구하고 매우 맛있고 달콤함
-선물용 우수한 패키징 — 패키지가 고퀄리티이고 큼직해 이벤트 경품이나 선물용으로 제격임</t>
+          <t>아르기닌과 밀크씨슬 조합 — 활력과 간 건강을 동시 케어할 수 있는 2개월분 세트 구성이 우수함
+피로 회복 및 운동 컨디션 — 섭취 후 아침 피로가 줄고 운동 집중도와 컨디션 유지에 도움이 됨
+쇼핑백 포함과 브랜드 신뢰 — 김종국 추천 제품으로 신뢰가 가며 쇼핑백이 포함되어 선물하기 좋음</t>
         </is>
       </c>
     </row>
@@ -4722,22 +4746,26 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>높고 상승하는 가격대 — 가격대가 다소 높은 편이며 지속적으로 가격이 올라 부담스러움</t>
+          <t>높은 가격대에 대한 부담 — 제품 품질은 우수하나 가격대가 다소 높게 느껴짐</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>배송 중 제품 해동 — 냉동 배송되어야 할 제품이 전부 녹아 도착함</t>
+          <t>다소 아쉬운 배송 속도 — 구성품은 만족스러우나 배송 일정이 약간 늦은 편임</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>다소 아쉬운 배송 속도 — 주문 후 배송 완료까지 시간이 다소 느린 편임</t>
+          <t>배송 중 제품 해동 발생 — 배송 과정에서 내용물이 다 녹아서 도착하는 문제점이 있음</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>단기 복용 시 효과 미체감 — 단기간 먹었을 때는 눈에 띄는 효과를 느끼기 어려움</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="inlineStr"/>
@@ -4761,14 +4789,14 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
+          <t>24,900원</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
           <t>64,200원</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>24,900원</t>
-        </is>
-      </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
           <t>28,900원</t>
@@ -4781,17 +4809,17 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
+          <t>33,200원</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>43,900원</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
           <t>29,900원</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>43,900원</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>33,200원</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -4986,7 +5014,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4994,58 +5022,54 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306201&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/NBw0phjtTvR7tEfBicGr032306201_00_01NBw0phjtTvR7tEfBicGr.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>2724</v>
+        <v>1277</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>저렴한 가격과 복용 편의 — 가격이 저렴하고 캡슐 형태로 먹기 편리함</t>
+          <t>저렴하고 합리적인 가격 — 가격 부담이 적어 다이어트 시 가볍게 구매하여 먹기 좋음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>원활한 배변 활동 촉진 — 복용 후 배변 활동이 원활해지는 효과를 봄</t>
+          <t>간편한 복용 편의성 — 섭취 방법이 간단하여 부담 없이 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>체감 효능의 개인차 — 다이어트나 체지방 감소 효능을 체감하지 못함</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5053,54 +5077,58 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
+          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953529&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=025575127&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/vXg1N5D0xbSNweDPvvl2994953529_00_00vXg1N5D0xbSNweDPvvl2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/VsX5iaJon2xHHTs8AQHv025575127_00_01VsX5iaJon2xHHTs8AQHv.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>365</v>
+        <v>886</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>저렴한 가격과 가성비 — 부담 없는 저렴한 가격으로 가성비가 훌륭함</t>
+          <t>부담 없는 가성비 — 가격 대비 구성이 괜찮아 가성비 좋게 구매 가능함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>진하고 상큼한 석류 맛 — 석류 맛이 진하고 새콤하여 맛있게 복용함</t>
+          <t>지속 복용 시 붓기 완화 — 매일 꾸준히 복용 시 붓기를 줄이는 데 도움을 느낌</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>붓기 개선 효과 미흡 — 사람에 따라 복용 후에도 체감되는 붓기 빼기 효과가 전혀 나타나지 않음</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5108,54 +5136,58 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[홍삼입문자] 자연관 6년근 홍삼정 에너타임 스탠다드 14포 14일분</t>
+          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762105&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911029&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260612/6YtHsleJV0YMOtFdtOAk901762105_00_016YtHsleJV0YMOtFdtOAk.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260623/QaObI3LjZ86tREQcCYCw610911029_00_00QaObI3LjZ86tREQcCYCw.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J4" t="n">
-        <v>211</v>
+        <v>479</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>입문자용 훌륭한 가성비 — 저렴한 가격으로 입문자가 부담 없이 체험해 보기 좋음</t>
+          <t>확실하고 빠른 배변 효과 — 복용 후 짧은 시간 안에 신호가 와서 변비 해소와 장 청소에 효과적임</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>여행용 휴대 적합성 — 포장 구성이 간편하여 여행 시 휴대해 가기 좋음</t>
+          <t>간편한 사용과 저렴한 가격 — 가격 대비 만족도가 높고 간편하게 식이섬유를 챙길 수 있음</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>목넘김 불편 및 효과 미흡 — 일부 복용 시 효과를 체감하기 어렵고 알약이 목에 걸려 불편함</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5163,12 +5195,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 유기농 야채분말 15포 15일분</t>
+          <t>대웅제약 콜라겐 60정 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5178,43 +5210,39 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157056&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000138&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260706/z42ScLP7B6TWURzgDPY0919157056_00_01z42ScLP7B6TWURzgDPY0.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/0buLkRj5uSU3KVXDKEhY600000138_00_000buLkRj5uSU3KVXDKEhY.png</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>379</v>
+        <v>1328</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>간편한 보름 분량 포장 — 하루 한 포씩 보름 동안 챙겨 먹기 편함</t>
+          <t>저렴한 가격과 뛰어난 가성비 — 다이소 제품으로 가격 부담이 적고 알뜰하게 콜라겐을 챙길 수 있음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>물에 타 먹기 쉬운 분말 — 분말 제형이라 물에 쉽게 타서 섭취 가능함</t>
+          <t>달콤한 맛과 간편한 복용 — 맛이 달콤하여 먹기 좋고 하루 2알씩 알약으로 삼키기 편함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>기호도 낮은 아쉬운 맛 — 간편함에 비해 맛이 너무 없어서 먹기 힘듦</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5222,45 +5250,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>종근당건강 브이퍼센트 멀티비타민 콜라겐샷 5포</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591591420&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911102&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250514/oMFpSUTevplZ5wvdXiLh591591420_00_00oMFpSUTevplZ5wvdXiLh.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/D3MtLfS4wvzyyoiG4ppT610911102_00_01D3MtLfS4wvzyyoiG4ppT.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J6" t="n">
-        <v>268</v>
+        <v>97</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>편안하고 맛있는 섭취 — 섭취하기가 편하고 맛이 우수하여 부담 없이 먹음</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>상쾌한 구강 케어 효과 — 터지면서 시원하고 상쾌한 느낌을 주어 식후 입냄새 제거에 좋음</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>상큼한 레몬 맛과 가성비 — 레몬 맛이 맛있으며 타사 제품 대비 가성비가 뛰어남</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>피부 효과 체감 미흡 및 당 함유 — 피부 미용 개선 효과를 체감하기 어렵고 당 성분이 포함되어 아쉬움</t>
+          <t>캡슐 겉껍질의 녹는 느낌 — 겉을 둘러싼 막이나 껍질이 잘 녹지 않아서 식감이 다소 애매함</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -5269,7 +5301,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5277,7 +5309,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 비타민B 30정 30일분</t>
+          <t>대웅제약 바나바잎 10정 10일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5287,33 +5319,33 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000129&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000278&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5QghHD5oyZssCfnGZbzA600000129_00_005QghHD5oyZssCfnGZbzA.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/uooE7Z5tFnMjhhremBna600000278_00_01uooE7Z5tFnMjhhremBna.png</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2222</v>
+        <v>718</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>복용이 편한 소형 알약 — 알약 크기가 크지 않아 목넘김이 수월함</t>
+          <t>혈당 관리 테스트에 적합 — 소량 구성으로 먼저 먹어보고 대용량을 결정하기에 용이함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>뛰어난 다이소 가성비 — 저렴한 가격대에 구매할 수 있어 주기적으로 재구매함</t>
+          <t>꾸준한 복용을 통한 케어 — 지속적으로 복용 시 마음의 위안을 주며 리뉴얼 후 효과를 체감함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -5324,7 +5356,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5332,46 +5364,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약 글루타치온 30정 30일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000130&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/0tJFRHjUfKCxN5mKhDV0600000130_00_000tJFRHjUfKCxN5mKhDV0.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1519</v>
+        <v>778</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>작은 크기와 뛰어난 휴대성 — 알약 크기가 작아 복용이 편하고 휴대하기 좋은 사이즈임</t>
+          <t>뛰어난 가성비 — 저렴한 가격으로 아르기닌을 부담 없이 구매할 수 있음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>저렴한 가격대 — 가격이 매우 저렴하여 부담 없이 지속 복용 가능함</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>피로 회복 및 체력 개선 — 섭취 시 확실히 덜 피곤하고 피로를 풀어주는 효과가 있음</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>물에 타 먹는 맛의 우수성 — 물에 타서 음료처럼 마실 때 맛이 우수하여 먹기 편함</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -5387,54 +5423,54 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
+          <t>[보령약국 X Pantio] 4050 에너지 올인원 12포 12일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>판티오</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=025575127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991014&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260605/VsX5iaJon2xHHTs8AQHv025575127_00_01VsX5iaJon2xHHTs8AQHv.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260805/nEaU2dcD2F8jaTQXSIb5033991014_00_00nEaU2dcD2F8jaTQXSIb5.png</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>885</v>
+        <v>65</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>부담 없는 가격 혜택 — 가격 대비 제품 구성이 저렴하여 혜자템으로 평가됨</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>간편한 올인원 3알 구성 — 1포에 영양제가 올인원으로 들어있어 따로 챙기지 않아도 되어 편리함</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>피로 회복 및 가성비 우수 — 가격 대비 구성이 알차며 지친 체력의 피로 회복을 도와줌</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>붓기 완화 효과 없음 — 정해진 용법대로 복용해도 붓기 개선 효과가 나타나지 않음</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5442,54 +5478,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 콜라겐 츄어블 28정 28일분</t>
+          <t>[옥수수수염＆호박] 동국제약 맛있는 센텔라 공주캔디 20정 20일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033574089&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911213&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260723/fiuR8VRO7LXZNa2zIgPd033574089_00_01fiuR8VRO7LXZNa2zIgPd.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/E3CpURjLLswf9MgzRChF610911213_00_01E3CpURjLLswf9MgzRChF.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J10" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>상큼하고 맛있는 맛 — 맛이 상큼하고 맛있어 거부감 없이 복용함</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>간편한 츄어블 제형 — 씹어 먹는 형태로 제공되어 간편하게 챙겨 먹기 좋음</t>
-        </is>
-      </c>
+          <t>상큼한 맛과 붓기 완화 — 상큼해서 간식처럼 먹기 좋으며 일부 붓기 완화에 효과를 봄</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>호불호 갈리는 맛과 식감 — 인위적인 맛과 푸석거리는 식감 때문에 입에 맞지 않아 버리기도 함</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>미비한 붓기 개선 효과 — 드라마틱한 효과를 기대하기 어려우며 붓기 완화 체감이 부족함</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5497,47 +5537,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 비타 15포 15일분</t>
+          <t>LG생활건강 이너뷰 루테인 지아잔틴 30캡슐</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910967&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953533&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260415/rKimZ2TE65XK1Rwibsnv610910967_00_02rKimZ2TE65XK1Rwibsnv.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/lXFnthJvrHdOJJvI4JC2994953533_00_00lXFnthJvrHdOJJvI4JC2.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1507</v>
+        <v>752</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>상큼한 과일 맛 — 과일 풍미가 나서 편하고 맛있게 먹을 수 있음</t>
+          <t>작아서 복용하기 쉬운 캡슐 — 캡슐 크기가 조그마하여 목넘김이 쉽고 부담 없이 먹을 수 있음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>만족스러운 가성비 — 가격이 적절하여 부담 없이 재구매하기 좋음</t>
+          <t>알찬 성분과 저렴한 할인 — 영양 성분 함량이 높고 행사 가격으로 저렴하게 구매 가능함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>명확한 효과 체감 미흡 — 꾸준히 복용해도 눈에 띄는 눈 건강 개선 효과를 느끼기 어려움</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -5652,52 +5696,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>피부/미용</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
     </row>
@@ -5709,52 +5753,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>판티오</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>이너뷰 바이 리튠</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>자연관</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>휴럼</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>셀트리온</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>이너뷰 바이 리튠</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
         </is>
       </c>
     </row>
@@ -5766,52 +5810,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
+          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[홍삼입문자] 자연관 6년근 홍삼정 에너타임 스탠다드 14포 14일분</t>
+          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 유기농 야채분말 15포 15일분</t>
+          <t>대웅제약 콜라겐 60정 30일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 브이퍼센트 멀티비타민 콜라겐샷 5포</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민B 30정 30일분</t>
+          <t>대웅제약 바나바잎 10정 10일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 글루타치온 30정 30일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
+          <t>[보령약국 X Pantio] 4050 에너지 올인원 12포 12일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 콜라겐 츄어블 28정 28일분</t>
+          <t>[옥수수수염＆호박] 동국제약 맛있는 센텔라 공주캔디 20정 20일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 비타 15포 15일분</t>
+          <t>LG생활건강 이너뷰 루테인 지아잔틴 30캡슐</t>
         </is>
       </c>
     </row>
@@ -5828,25 +5872,25 @@
         <v>4.7</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>4.7</v>
-      </c>
       <c r="G6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.8</v>
@@ -5859,37 +5903,37 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2724</v>
+        <v>1277</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>365</v>
+        <v>886</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>211</v>
+        <v>479</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>379</v>
+        <v>1328</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>268</v>
+        <v>97</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2222</v>
+        <v>718</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1519</v>
+        <v>778</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>885</v>
+        <v>65</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1507</v>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -5897,95 +5941,102 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 가격과 복용 편의 — 가격이 저렴하고 캡슐 형태로 먹기 편리함
-원활한 배변 활동 촉진 — 복용 후 배변 활동이 원활해지는 효과를 봄</t>
+          <t>저렴하고 합리적인 가격 — 가격 부담이 적어 다이어트 시 가볍게 구매하여 먹기 좋음
+간편한 복용 편의성 — 섭취 방법이 간단하여 부담 없이 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 가격과 가성비 — 부담 없는 저렴한 가격으로 가성비가 훌륭함
-진하고 상큼한 석류 맛 — 석류 맛이 진하고 새콤하여 맛있게 복용함</t>
+          <t>부담 없는 가성비 — 가격 대비 구성이 괜찮아 가성비 좋게 구매 가능함
+지속 복용 시 붓기 완화 — 매일 꾸준히 복용 시 붓기를 줄이는 데 도움을 느낌</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>입문자용 훌륭한 가성비 — 저렴한 가격으로 입문자가 부담 없이 체험해 보기 좋음
-여행용 휴대 적합성 — 포장 구성이 간편하여 여행 시 휴대해 가기 좋음</t>
+          <t>확실하고 빠른 배변 효과 — 복용 후 짧은 시간 안에 신호가 와서 변비 해소와 장 청소에 효과적임
+간편한 사용과 저렴한 가격 — 가격 대비 만족도가 높고 간편하게 식이섬유를 챙길 수 있음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>간편한 보름 분량 포장 — 하루 한 포씩 보름 동안 챙겨 먹기 편함
-물에 타 먹기 쉬운 분말 — 분말 제형이라 물에 쉽게 타서 섭취 가능함</t>
+          <t>저렴한 가격과 뛰어난 가성비 — 다이소 제품으로 가격 부담이 적고 알뜰하게 콜라겐을 챙길 수 있음
+달콤한 맛과 간편한 복용 — 맛이 달콤하여 먹기 좋고 하루 2알씩 알약으로 삼키기 편함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>편안하고 맛있는 섭취 — 섭취하기가 편하고 맛이 우수하여 부담 없이 먹음</t>
+          <t>상쾌한 구강 케어 효과 — 터지면서 시원하고 상쾌한 느낌을 주어 식후 입냄새 제거에 좋음
+상큼한 레몬 맛과 가성비 — 레몬 맛이 맛있으며 타사 제품 대비 가성비가 뛰어남</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>복용이 편한 소형 알약 — 알약 크기가 크지 않아 목넘김이 수월함
-뛰어난 다이소 가성비 — 저렴한 가격대에 구매할 수 있어 주기적으로 재구매함</t>
+          <t>혈당 관리 테스트에 적합 — 소량 구성으로 먼저 먹어보고 대용량을 결정하기에 용이함
+꾸준한 복용을 통한 케어 — 지속적으로 복용 시 마음의 위안을 주며 리뉴얼 후 효과를 체감함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>작은 크기와 뛰어난 휴대성 — 알약 크기가 작아 복용이 편하고 휴대하기 좋은 사이즈임
-저렴한 가격대 — 가격이 매우 저렴하여 부담 없이 지속 복용 가능함</t>
+          <t>뛰어난 가성비 — 저렴한 가격으로 아르기닌을 부담 없이 구매할 수 있음
+피로 회복 및 체력 개선 — 섭취 시 확실히 덜 피곤하고 피로를 풀어주는 효과가 있음
+물에 타 먹는 맛의 우수성 — 물에 타서 음료처럼 마실 때 맛이 우수하여 먹기 편함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 가격 혜택 — 가격 대비 제품 구성이 저렴하여 혜자템으로 평가됨</t>
+          <t>간편한 올인원 3알 구성 — 1포에 영양제가 올인원으로 들어있어 따로 챙기지 않아도 되어 편리함
+피로 회복 및 가성비 우수 — 가격 대비 구성이 알차며 지친 체력의 피로 회복을 도와줌</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>상큼하고 맛있는 맛 — 맛이 상큼하고 맛있어 거부감 없이 복용함
-간편한 츄어블 제형 — 씹어 먹는 형태로 제공되어 간편하게 챙겨 먹기 좋음</t>
+          <t>상큼한 맛과 붓기 완화 — 상큼해서 간식처럼 먹기 좋으며 일부 붓기 완화에 효과를 봄</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>상큼한 과일 맛 — 과일 풍미가 나서 편하고 맛있게 먹을 수 있음
-만족스러운 가성비 — 가격이 적절하여 부담 없이 재구매하기 좋음</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>작아서 복용하기 쉬운 캡슐 — 캡슐 크기가 조그마하여 목넘김이 쉽고 부담 없이 먹을 수 있음
+알찬 성분과 저렴한 할인 — 영양 성분 함량이 높고 행사 가격으로 저렴하게 구매 가능함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>체감 효능의 개인차 — 다이어트나 체지방 감소 효능을 체감하지 못함</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>기호도 낮은 아쉬운 맛 — 간편함에 비해 맛이 너무 없어서 먹기 힘듦</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>붓기 개선 효과 미흡 — 사람에 따라 복용 후에도 체감되는 붓기 빼기 효과가 전혀 나타나지 않음</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>목넘김 불편 및 효과 미흡 — 일부 복용 시 효과를 체감하기 어렵고 알약이 목에 걸려 불편함</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>피부 효과 체감 미흡 및 당 함유 — 피부 미용 개선 효과를 체감하기 어렵고 당 성분이 포함되어 아쉬움</t>
+          <t>캡슐 겉껍질의 녹는 느낌 — 겉을 둘러싼 막이나 껍질이 잘 녹지 않아서 식감이 다소 애매함</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>붓기 완화 효과 없음 — 정해진 용법대로 복용해도 붓기 개선 효과가 나타나지 않음</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>호불호 갈리는 맛과 식감 — 인위적인 맛과 푸석거리는 식감 때문에 입에 맞지 않아 버리기도 함
+미비한 붓기 개선 효과 — 드라마틱한 효과를 기대하기 어려우며 붓기 완화 체감이 부족함</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>명확한 효과 체감 미흡 — 꾸준히 복용해도 눈에 띄는 눈 건강 개선 효과를 느끼기 어려움</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -5995,52 +6046,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>1,500원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
         </is>
       </c>
     </row>
@@ -6219,7 +6270,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6227,27 +6278,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
+          <t>[산리오콜라보/9월올영픽] 비비랩 화이트 콜라겐 헬로키티 기획/석류콜라겐 마이멜로디 기획 (+마켓백 증정)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>딥트3일</t>
+          <t>비비랩</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16,000원</t>
+          <t>11,400원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000211396&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248072&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021139617ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024807238ko.png?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -6262,7 +6313,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6270,27 +6321,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[산리오콜라보/9월올영픽] 비비랩 화이트 콜라겐 헬로키티 기획/석류콜라겐 마이멜로디 기획 (+마켓백 증정)</t>
+          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>비비랩</t>
+          <t>코자아</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>11,400원</t>
+          <t>32,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248072&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236755&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024807238ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023675540ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -6305,7 +6356,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6313,27 +6364,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000219379&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021937922ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -6348,7 +6399,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6356,27 +6407,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>닥터아돌 B발라민 비오틴 120정 (2개월분)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>닥터아돌</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30,600원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000231625&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023162516ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -6391,7 +6442,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6399,27 +6450,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -6434,7 +6485,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6442,27 +6493,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -6508,27 +6559,11 @@
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014345ko.jpg?l=ko</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>12729</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>귀여운 산리오 증정품 — 산리오 콜라보 러기지택 굿즈 구성으로 소장 가치가 높음</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>복통 없는 배변 활동 — 배 아픔이나 가스 차는 현상 없이 편안하게 화장실을 감</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>하루 한 포의 간편함 — 1일 1포 개별 스틱으로 바쁜 일상 속 장 건강 관리가 용이함</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -6536,7 +6571,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6544,45 +6579,33 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>519</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>장 케어와 다이어트 동시 관리 — 장 건강과 체지방 감소를 함께 관리하는 이중 기능성 제품임</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>상큼한 요거트 맛 — 상큼한 요거트 맛으로 하루 한 포씩 맛있게 먹기 좋음</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -6591,7 +6614,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6599,50 +6622,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
+          <t>[9월 올영픽/급찐급빠] 칼로 스탑/컨트롤 PLUS 15포+15포 (+폼폼푸린 키링) / 더블기획 3종</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>칼로(Kalo)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229934&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000243670&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022993425ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2155</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>귀여운 산리오 콜라보 굿즈 — 키링, 카라비너 등 귀여운 캐릭터 굿즈가 동봉됨</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>맛있는 탱글 젤리 식감 — 새콤달콤한 맛과 치아씨드 식감으로 간식처럼 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>변비 개선 효과 — 아랫배 답답함이나 만성 변비 완화에 도움을 줌</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024367012ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -6650,7 +6657,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6658,50 +6665,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (60일분)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000164736&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0016/A00000016473623ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>15433</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>신속한 입면 및 숙면 유도 — 자기 전 복용 시 빠르게 푹 잠들 수 있게 도와줌</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>물 없는 구미 형태 — 약 맛 없는 맛있는 젤리 형태라 침대 옆에 두고 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>식물성 성분의 안심감 — 식물성 멜라토닌 성분을 사용하여 부담 없이 복용함</t>
-        </is>
-      </c>
+        <v>15718</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -6817,52 +6812,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
     </row>
@@ -6874,34 +6869,34 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>딥트3일</t>
+          <t>비비랩</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>비비랩</t>
+          <t>코자아</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>닥터아돌</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>지노마스터</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
-        </is>
-      </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
           <t>바이오코어유산균</t>
@@ -6909,17 +6904,17 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>칼로(Kalo)</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>고려은단</t>
         </is>
       </c>
     </row>
@@ -6931,34 +6926,34 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
+          <t>[산리오콜라보/9월올영픽] 비비랩 화이트 콜라겐 헬로키티 기획/석류콜라겐 마이멜로디 기획 (+마켓백 증정)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>[산리오콜라보/9월올영픽] 비비랩 화이트 콜라겐 헬로키티 기획/석류콜라겐 마이멜로디 기획 (+마켓백 증정)</t>
+          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>닥터아돌 B발라민 비오틴 120정 (2개월분)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
           <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
-        </is>
-      </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
           <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
@@ -6966,17 +6961,17 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
+          <t>[9월 올영픽/급찐급빠] 칼로 스탑/컨트롤 PLUS 15포+15포 (+폼폼푸린 키링) / 더블기획 3종</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (60일분)</t>
         </is>
       </c>
     </row>
@@ -6992,17 +6987,11 @@
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>4.6</v>
-      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
       <c r="L6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="7">
@@ -7017,20 +7006,14 @@
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="n">
-        <v>12729</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>519</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>2155</v>
-      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="n">
-        <v>15433</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>15718</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -7042,33 +7025,10 @@
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>귀여운 산리오 증정품 — 산리오 콜라보 러기지택 굿즈 구성으로 소장 가치가 높음
-복통 없는 배변 활동 — 배 아픔이나 가스 차는 현상 없이 편안하게 화장실을 감
-하루 한 포의 간편함 — 1일 1포 개별 스틱으로 바쁜 일상 속 장 건강 관리가 용이함</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>장 케어와 다이어트 동시 관리 — 장 건강과 체지방 감소를 함께 관리하는 이중 기능성 제품임
-상큼한 요거트 맛 — 상큼한 요거트 맛으로 하루 한 포씩 맛있게 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>귀여운 산리오 콜라보 굿즈 — 키링, 카라비너 등 귀여운 캐릭터 굿즈가 동봉됨
-맛있는 탱글 젤리 식감 — 새콤달콤한 맛과 치아씨드 식감으로 간식처럼 먹기 좋음
-변비 개선 효과 — 아랫배 답답함이나 만성 변비 완화에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>신속한 입면 및 숙면 유도 — 자기 전 복용 시 빠르게 푹 잠들 수 있게 도와줌
-물 없는 구미 형태 — 약 맛 없는 맛있는 젤리 형태라 침대 옆에 두고 먹기 편함
-식물성 성분의 안심감 — 식물성 멜라토닌 성분을 사용하여 부담 없이 복용함</t>
-        </is>
-      </c>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -7095,34 +7055,34 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>16,000원</t>
+          <t>11,400원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>11,400원</t>
+          <t>32,900원</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>30,600원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
           <t>27,400원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>17,900원</t>
-        </is>
-      </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
           <t>13,950원</t>
@@ -7130,17 +7090,17 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>10,900원</t>
         </is>
       </c>
     </row>
@@ -7228,7 +7188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7270,16 +7230,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
         <v>5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
@@ -7288,29 +7248,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>22.5</v>
+        <v>27.5</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -7320,13 +7280,13 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7336,25 +7296,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -7364,19 +7324,19 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -7389,10 +7349,54 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="n">
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
